--- a/python/scripts/oracle_upload/sectors.xlsx
+++ b/python/scripts/oracle_upload/sectors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AD_ACCEL_HE\preRelease\RDB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AD_ACCEL\20261014s\RDB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAFAD30A-4D35-45CE-B291-C8CD3AF4CF08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8573CF49-38FF-4166-8A8B-2615C1158284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25665" yWindow="2460" windowWidth="22710" windowHeight="16245" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11460" yWindow="1620" windowWidth="14955" windowHeight="18510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="scS" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="410">
   <si>
     <t>S00</t>
   </si>
@@ -240,6 +240,9 @@
     <t>areas</t>
   </si>
   <si>
+    <t>DOG</t>
+  </si>
+  <si>
     <t>BYP/SPD1</t>
   </si>
   <si>
@@ -273,9 +276,6 @@
     <t>DMPH</t>
   </si>
   <si>
-    <t>GUN1/GUN2/L0/HTR/EMIT/BX0</t>
-  </si>
-  <si>
     <t>L2/BC2</t>
   </si>
   <si>
@@ -1020,15 +1020,15 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>CLTH/BSYH1/BSYH2</t>
-  </si>
-  <si>
     <t>BEGL1</t>
   </si>
   <si>
     <t>ENDBC2</t>
   </si>
   <si>
+    <t>Sector boundaries from "Beamline Boundaries" PRD (LCLSII-2.1-PR-0134-R5)</t>
+  </si>
+  <si>
     <t>BEGGUN</t>
   </si>
   <si>
@@ -1134,31 +1134,154 @@
     <t>ENDSXTES_3</t>
   </si>
   <si>
+    <t>CBXFEL chicane #2</t>
+  </si>
+  <si>
+    <t>HXRSS chicane</t>
+  </si>
+  <si>
+    <t>SXRSS chicane</t>
+  </si>
+  <si>
+    <t>ENDESA</t>
+  </si>
+  <si>
+    <t>ESA</t>
+  </si>
+  <si>
+    <t>ENDBSYA</t>
+  </si>
+  <si>
+    <t>CLTH/BSYH</t>
+  </si>
+  <si>
+    <t>ENDBSYH</t>
+  </si>
+  <si>
+    <t>partial cell</t>
+  </si>
+  <si>
+    <t>comment</t>
+  </si>
+  <si>
+    <t>CBXFEL chicane #1</t>
+  </si>
+  <si>
+    <t>contains</t>
+  </si>
+  <si>
+    <t>Delta-II</t>
+  </si>
+  <si>
+    <t>overlay</t>
+  </si>
+  <si>
+    <t>SPH</t>
+  </si>
+  <si>
+    <t>SPA</t>
+  </si>
+  <si>
+    <t>SLTD</t>
+  </si>
+  <si>
+    <t>SLTA</t>
+  </si>
+  <si>
+    <t>BYP/SPH</t>
+  </si>
+  <si>
+    <t>SPD1/SPD2/SPD3</t>
+  </si>
+  <si>
+    <t>SPD3</t>
+  </si>
+  <si>
+    <t>SPD1/SPD2/SPA</t>
+  </si>
+  <si>
+    <t>ENDSLTA</t>
+  </si>
+  <si>
+    <t>SLTH/BSYH</t>
+  </si>
+  <si>
+    <t>BEGBSYA</t>
+  </si>
+  <si>
+    <t>BEGCLTS</t>
+  </si>
+  <si>
+    <t>ENDCLTS</t>
+  </si>
+  <si>
+    <t>CLTS</t>
+  </si>
+  <si>
+    <t>BSY coordinates</t>
+  </si>
+  <si>
+    <t>ENDGSPEC</t>
+  </si>
+  <si>
+    <t>GUN/L0/HTR/EMIT/BX0</t>
+  </si>
+  <si>
+    <t>SPEC</t>
+  </si>
+  <si>
+    <t>GSPEC</t>
+  </si>
+  <si>
+    <t>BEGGSPEC</t>
+  </si>
+  <si>
+    <t>BEGSPEC</t>
+  </si>
+  <si>
+    <t>ENDSPEC</t>
+  </si>
+  <si>
+    <t>GUNLEI/L0LEI/LEI1/LEI2</t>
+  </si>
+  <si>
+    <t>BEGGUNLEI</t>
+  </si>
+  <si>
+    <t>LEI2</t>
+  </si>
+  <si>
+    <t>ENDLEI_2</t>
+  </si>
+  <si>
+    <t>BEGDIAGIS</t>
+  </si>
+  <si>
+    <t>DIAGIS</t>
+  </si>
+  <si>
+    <t>ENDDIAGIS</t>
+  </si>
+  <si>
+    <t>S09</t>
+  </si>
+  <si>
     <t>L4B</t>
   </si>
   <si>
-    <t>S09</t>
-  </si>
-  <si>
     <t>S10</t>
   </si>
   <si>
+    <t>L4B/EXT/DOG</t>
+  </si>
+  <si>
     <t>S11</t>
   </si>
   <si>
-    <t>9 cells</t>
-  </si>
-  <si>
-    <t>8 cells</t>
-  </si>
-  <si>
-    <t>PREUNDH,HXR</t>
-  </si>
-  <si>
-    <t>11 cells</t>
-  </si>
-  <si>
-    <t>Sector boundaries from "Beamline Boundaries" PRD (LCLSII-HE-1.3-PR-0028-R0)</t>
+    <t>L3B/BR3B/L4B</t>
+  </si>
+  <si>
+    <t>SXR cell 16</t>
   </si>
   <si>
     <t>SXR cell 17</t>
@@ -1186,147 +1309,6 @@
   </si>
   <si>
     <t>SXR cell 25</t>
-  </si>
-  <si>
-    <t>PREUNDH</t>
-  </si>
-  <si>
-    <t>L3B/BR3B/L4B</t>
-  </si>
-  <si>
-    <t>L4B/EXT/DOG</t>
-  </si>
-  <si>
-    <t>DOG</t>
-  </si>
-  <si>
-    <t>CLTS</t>
-  </si>
-  <si>
-    <t>BEGCLTS</t>
-  </si>
-  <si>
-    <t>ENDCLTS</t>
-  </si>
-  <si>
-    <t>overlay</t>
-  </si>
-  <si>
-    <t>GSPEC</t>
-  </si>
-  <si>
-    <t>BEGGSPEC</t>
-  </si>
-  <si>
-    <t>ENDGSPEC</t>
-  </si>
-  <si>
-    <t>SPEC</t>
-  </si>
-  <si>
-    <t>BEGSPEC</t>
-  </si>
-  <si>
-    <t>ENDSPEC</t>
-  </si>
-  <si>
-    <t>ENDBSYH</t>
-  </si>
-  <si>
-    <t>ESA</t>
-  </si>
-  <si>
-    <t>ENDBSYA</t>
-  </si>
-  <si>
-    <t>ENDESA</t>
-  </si>
-  <si>
-    <t>BEGBSYA</t>
-  </si>
-  <si>
-    <t>BYP/SPH</t>
-  </si>
-  <si>
-    <t>SPH</t>
-  </si>
-  <si>
-    <t>SPD1/SPD2/SPD3</t>
-  </si>
-  <si>
-    <t>SPD1/SPD2/SPA</t>
-  </si>
-  <si>
-    <t>SPD3</t>
-  </si>
-  <si>
-    <t>SPA</t>
-  </si>
-  <si>
-    <t>SLTH/BSYH</t>
-  </si>
-  <si>
-    <t>SLTD</t>
-  </si>
-  <si>
-    <t>SLTA</t>
-  </si>
-  <si>
-    <t>ENDSLTA</t>
-  </si>
-  <si>
-    <t>SXX cell 16</t>
-  </si>
-  <si>
-    <t>partial cell</t>
-  </si>
-  <si>
-    <t>contains</t>
-  </si>
-  <si>
-    <t>comment</t>
-  </si>
-  <si>
-    <t>SXRSS chicane</t>
-  </si>
-  <si>
-    <t>Delta-II</t>
-  </si>
-  <si>
-    <t>CBXFEL chicane #1</t>
-  </si>
-  <si>
-    <t>CBXFEL chicane #2</t>
-  </si>
-  <si>
-    <t>HXRSS chicane</t>
-  </si>
-  <si>
-    <t>GUNLEI/L0LEI/LEI1/LEI2</t>
-  </si>
-  <si>
-    <t>BEGGUNLEI</t>
-  </si>
-  <si>
-    <t>LEI2</t>
-  </si>
-  <si>
-    <t>ENDLEI_2</t>
-  </si>
-  <si>
-    <t>DIAGI1</t>
-  </si>
-  <si>
-    <t>BEGDIAGI_1</t>
-  </si>
-  <si>
-    <t>DIAGI1/DIAGI1</t>
-  </si>
-  <si>
-    <t>ENDDIAGI_2</t>
-  </si>
-  <si>
-    <t>BEGESA</t>
   </si>
 </sst>
 </file>
@@ -1515,14 +1497,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1822,8 +1804,10 @@
     <col min="4" max="4" width="24.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="16.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.42578125" customWidth="1"/>
     <col min="12" max="12" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -1912,7 +1896,7 @@
       <c r="I4" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="K4" s="24" t="s">
+      <c r="K4" s="25" t="s">
         <v>28</v>
       </c>
       <c r="L4" s="1">
@@ -1948,7 +1932,7 @@
         <f t="shared" ref="H5:H34" si="4">G5/0.3048</f>
         <v>333.33333333333331</v>
       </c>
-      <c r="K5" s="24"/>
+      <c r="K5" s="25"/>
       <c r="L5" s="1">
         <v>2</v>
       </c>
@@ -1982,7 +1966,7 @@
         <f t="shared" si="4"/>
         <v>333.33333333333331</v>
       </c>
-      <c r="K6" s="24"/>
+      <c r="K6" s="25"/>
       <c r="L6" s="1">
         <v>3</v>
       </c>
@@ -2016,7 +2000,7 @@
         <f t="shared" si="4"/>
         <v>333.3333333333332</v>
       </c>
-      <c r="K7" s="24"/>
+      <c r="K7" s="25"/>
       <c r="L7" s="1">
         <v>4</v>
       </c>
@@ -2050,7 +2034,7 @@
         <f t="shared" si="4"/>
         <v>333.33333333333337</v>
       </c>
-      <c r="K8" s="24"/>
+      <c r="K8" s="25"/>
       <c r="L8" s="1">
         <v>5</v>
       </c>
@@ -2084,7 +2068,7 @@
         <f t="shared" si="4"/>
         <v>333.33333333333337</v>
       </c>
-      <c r="K9" s="24"/>
+      <c r="K9" s="25"/>
       <c r="L9" s="1">
         <v>6</v>
       </c>
@@ -2118,7 +2102,7 @@
         <f t="shared" si="4"/>
         <v>333.33333333333303</v>
       </c>
-      <c r="K10" s="24"/>
+      <c r="K10" s="25"/>
       <c r="L10" s="1">
         <v>7</v>
       </c>
@@ -2134,7 +2118,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>370</v>
+        <v>399</v>
       </c>
       <c r="E11" s="3">
         <f t="shared" si="2"/>
@@ -2152,7 +2136,7 @@
         <f t="shared" si="4"/>
         <v>333.33333333333337</v>
       </c>
-      <c r="K11" s="24"/>
+      <c r="K11" s="25"/>
       <c r="L11" s="1">
         <v>8</v>
       </c>
@@ -2168,7 +2152,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>351</v>
+        <v>395</v>
       </c>
       <c r="E12" s="3">
         <f t="shared" si="2"/>
@@ -2186,14 +2170,14 @@
         <f t="shared" si="4"/>
         <v>333.33333333333337</v>
       </c>
-      <c r="K12" s="24"/>
+      <c r="K12" s="25"/>
       <c r="L12" s="1">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>352</v>
+        <v>394</v>
       </c>
       <c r="B13" s="1">
         <v>1</v>
@@ -2202,7 +2186,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>351</v>
+        <v>395</v>
       </c>
       <c r="E13" s="3">
         <f t="shared" si="2"/>
@@ -2222,14 +2206,14 @@
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="9"/>
-      <c r="K13" s="24"/>
+      <c r="K13" s="25"/>
       <c r="L13" s="1">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>353</v>
+        <v>396</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
@@ -2238,7 +2222,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>371</v>
+        <v>397</v>
       </c>
       <c r="E14" s="3">
         <f t="shared" si="2"/>
@@ -2258,14 +2242,14 @@
       </c>
       <c r="I14" s="9"/>
       <c r="J14" s="9"/>
-      <c r="K14" s="24"/>
+      <c r="K14" s="25"/>
       <c r="L14" s="1">
         <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>354</v>
+        <v>398</v>
       </c>
       <c r="B15" s="1">
         <v>1</v>
@@ -2274,7 +2258,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>372</v>
+        <v>53</v>
       </c>
       <c r="E15" s="3">
         <f t="shared" si="2"/>
@@ -2294,7 +2278,7 @@
       </c>
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
-      <c r="K15" s="24"/>
+      <c r="K15" s="25"/>
       <c r="L15" s="1">
         <v>12</v>
       </c>
@@ -2332,7 +2316,7 @@
       <c r="J16" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="K16" s="24"/>
+      <c r="K16" s="25"/>
       <c r="L16" s="1">
         <v>13</v>
       </c>
@@ -2372,7 +2356,7 @@
       <c r="J17" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="K17" s="24"/>
+      <c r="K17" s="25"/>
       <c r="L17" s="1">
         <v>14</v>
       </c>
@@ -2412,7 +2396,7 @@
       <c r="J18" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="K18" s="24"/>
+      <c r="K18" s="25"/>
       <c r="L18" s="1">
         <v>15</v>
       </c>
@@ -2452,7 +2436,7 @@
       <c r="J19" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="K19" s="24"/>
+      <c r="K19" s="25"/>
       <c r="L19" s="1">
         <v>16</v>
       </c>
@@ -2492,7 +2476,7 @@
       <c r="J20" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="K20" s="24"/>
+      <c r="K20" s="25"/>
       <c r="L20" s="1">
         <v>17</v>
       </c>
@@ -2532,7 +2516,7 @@
       <c r="J21" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="K21" s="24"/>
+      <c r="K21" s="25"/>
       <c r="L21" s="1">
         <v>18</v>
       </c>
@@ -2572,7 +2556,7 @@
       <c r="J22" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="K22" s="24"/>
+      <c r="K22" s="25"/>
       <c r="L22" s="1">
         <v>19</v>
       </c>
@@ -2612,7 +2596,7 @@
       <c r="J23" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="K23" s="24"/>
+      <c r="K23" s="25"/>
       <c r="L23" s="1">
         <v>20</v>
       </c>
@@ -2652,7 +2636,7 @@
       <c r="J24" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="K24" s="24"/>
+      <c r="K24" s="25"/>
       <c r="L24" s="1">
         <v>21</v>
       </c>
@@ -2692,7 +2676,7 @@
       <c r="J25" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="K25" s="24"/>
+      <c r="K25" s="25"/>
       <c r="L25" s="1">
         <v>22</v>
       </c>
@@ -2732,7 +2716,7 @@
       <c r="J26" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="K26" s="24"/>
+      <c r="K26" s="25"/>
       <c r="L26" s="1">
         <v>23</v>
       </c>
@@ -2772,7 +2756,7 @@
       <c r="J27" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="K27" s="24"/>
+      <c r="K27" s="25"/>
       <c r="L27" s="1">
         <v>24</v>
       </c>
@@ -2812,7 +2796,7 @@
       <c r="J28" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="K28" s="24"/>
+      <c r="K28" s="25"/>
       <c r="L28" s="1">
         <v>25</v>
       </c>
@@ -2852,7 +2836,7 @@
       <c r="J29" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="K29" s="24"/>
+      <c r="K29" s="25"/>
       <c r="L29" s="1">
         <v>26</v>
       </c>
@@ -2892,7 +2876,7 @@
       <c r="J30" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="K30" s="24"/>
+      <c r="K30" s="25"/>
       <c r="L30" s="1">
         <v>27</v>
       </c>
@@ -2932,7 +2916,7 @@
       <c r="J31" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="K31" s="24"/>
+      <c r="K31" s="25"/>
       <c r="L31" s="1">
         <v>28</v>
       </c>
@@ -2948,7 +2932,7 @@
         <v>0</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E32" s="3">
         <f t="shared" si="2"/>
@@ -2966,12 +2950,12 @@
         <f t="shared" si="4"/>
         <v>333.33333333333303</v>
       </c>
-      <c r="K32" s="24"/>
+      <c r="K32" s="25"/>
       <c r="L32" s="1">
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
         <v>18</v>
       </c>
@@ -2982,7 +2966,7 @@
         <v>0</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E33" s="3">
         <f t="shared" si="2"/>
@@ -3000,12 +2984,12 @@
         <f t="shared" si="4"/>
         <v>333.33333333333303</v>
       </c>
-      <c r="K33" s="24"/>
+      <c r="K33" s="25"/>
       <c r="L33" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="16" t="s">
         <v>19</v>
       </c>
@@ -3037,12 +3021,12 @@
       <c r="J34" s="18" t="s">
         <v>301</v>
       </c>
-      <c r="K34" s="25"/>
+      <c r="K34" s="26"/>
       <c r="L34" s="1">
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="21" t="s">
         <v>20</v>
       </c>
@@ -3053,7 +3037,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E35" s="22">
         <v>2.512</v>
@@ -3075,14 +3059,14 @@
       <c r="J35" s="21" t="s">
         <v>303</v>
       </c>
-      <c r="K35" s="26" t="s">
+      <c r="K35" s="27" t="s">
         <v>29</v>
       </c>
       <c r="L35" s="1">
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>82</v>
       </c>
@@ -3093,7 +3077,7 @@
         <v>1</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E36" s="3">
         <f t="shared" ref="E36:E53" si="7">F35</f>
@@ -3113,12 +3097,12 @@
       <c r="I36" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="K36" s="24"/>
+      <c r="K36" s="25"/>
       <c r="L36" s="1">
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>83</v>
       </c>
@@ -3129,7 +3113,7 @@
         <v>1</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E37" s="3">
         <f t="shared" si="7"/>
@@ -3146,12 +3130,12 @@
         <f t="shared" si="6"/>
         <v>85.171587926509247</v>
       </c>
-      <c r="K37" s="24"/>
+      <c r="K37" s="25"/>
       <c r="L37" s="1">
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>84</v>
       </c>
@@ -3162,7 +3146,7 @@
         <v>1</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E38" s="3">
         <f t="shared" si="7"/>
@@ -3179,12 +3163,12 @@
         <f t="shared" si="6"/>
         <v>90.504265091863431</v>
       </c>
-      <c r="K38" s="24"/>
+      <c r="K38" s="25"/>
       <c r="L38" s="1">
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>85</v>
       </c>
@@ -3195,7 +3179,7 @@
         <v>1</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E39" s="3">
         <f t="shared" si="7"/>
@@ -3212,12 +3196,12 @@
         <f t="shared" si="6"/>
         <v>100.17946194225736</v>
       </c>
-      <c r="K39" s="24"/>
+      <c r="K39" s="25"/>
       <c r="L39" s="1">
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>86</v>
       </c>
@@ -3228,7 +3212,7 @@
         <v>1</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E40" s="3">
         <f t="shared" si="7"/>
@@ -3245,12 +3229,12 @@
         <f t="shared" si="6"/>
         <v>89.236876640419837</v>
       </c>
-      <c r="K40" s="24"/>
+      <c r="K40" s="25"/>
       <c r="L40" s="1">
         <v>37</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>87</v>
       </c>
@@ -3261,7 +3245,7 @@
         <v>1</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E41" s="3">
         <f t="shared" si="7"/>
@@ -3278,12 +3262,12 @@
         <f t="shared" si="6"/>
         <v>90.484908136482858</v>
       </c>
-      <c r="K41" s="24"/>
+      <c r="K41" s="25"/>
       <c r="L41" s="1">
         <v>38</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>88</v>
       </c>
@@ -3294,7 +3278,7 @@
         <v>1</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E42" s="3">
         <f t="shared" si="7"/>
@@ -3311,12 +3295,12 @@
         <f t="shared" si="6"/>
         <v>75.762795275590648</v>
       </c>
-      <c r="K42" s="24"/>
+      <c r="K42" s="25"/>
       <c r="L42" s="1">
         <v>39</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>89</v>
       </c>
@@ -3327,7 +3311,7 @@
         <v>1</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E43" s="3">
         <f t="shared" si="7"/>
@@ -3344,12 +3328,12 @@
         <f t="shared" si="6"/>
         <v>95.227034120734857</v>
       </c>
-      <c r="K43" s="24"/>
+      <c r="K43" s="25"/>
       <c r="L43" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>90</v>
       </c>
@@ -3360,7 +3344,7 @@
         <v>1</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E44" s="3">
         <f t="shared" si="7"/>
@@ -3377,12 +3361,12 @@
         <f t="shared" si="6"/>
         <v>99.886811023622172</v>
       </c>
-      <c r="K44" s="24"/>
+      <c r="K44" s="25"/>
       <c r="L44" s="1">
         <v>41</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>91</v>
       </c>
@@ -3393,7 +3377,7 @@
         <v>1</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E45" s="3">
         <f t="shared" si="7"/>
@@ -3410,12 +3394,12 @@
         <f t="shared" si="6"/>
         <v>88.113845144356958</v>
       </c>
-      <c r="K45" s="24"/>
+      <c r="K45" s="25"/>
       <c r="L45" s="1">
         <v>42</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>92</v>
       </c>
@@ -3426,7 +3410,7 @@
         <v>1</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E46" s="3">
         <f t="shared" si="7"/>
@@ -3443,12 +3427,12 @@
         <f t="shared" si="6"/>
         <v>95.997703412073378</v>
       </c>
-      <c r="K46" s="24"/>
+      <c r="K46" s="25"/>
       <c r="L46" s="1">
         <v>43</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>93</v>
       </c>
@@ -3459,7 +3443,7 @@
         <v>1</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E47" s="3">
         <f t="shared" si="7"/>
@@ -3479,12 +3463,12 @@
       <c r="J47" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="K47" s="24"/>
+      <c r="K47" s="25"/>
       <c r="L47" s="1">
         <v>44</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>96</v>
       </c>
@@ -3495,7 +3479,7 @@
         <v>1</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E48" s="3">
         <f t="shared" si="7"/>
@@ -3505,25 +3489,22 @@
         <v>559.58649200000002</v>
       </c>
       <c r="G48" s="3">
-        <f t="shared" ref="G48:G61" si="8">F48-E48</f>
+        <f t="shared" ref="G48:G58" si="8">F48-E48</f>
         <v>41.929491999999982</v>
       </c>
       <c r="H48" s="3">
-        <f t="shared" ref="H48:H61" si="9">G48/0.3048</f>
+        <f t="shared" ref="H48:H57" si="9">G48/0.3048</f>
         <v>137.56395013123353</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="K48" s="24"/>
+      <c r="K48" s="25"/>
       <c r="L48" s="1">
         <v>45</v>
       </c>
-      <c r="N48" s="6" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>97</v>
       </c>
@@ -3534,7 +3515,7 @@
         <v>1</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E49" s="3">
         <f t="shared" si="7"/>
@@ -3551,15 +3532,12 @@
         <f t="shared" si="9"/>
         <v>115.48556430446172</v>
       </c>
-      <c r="K49" s="24"/>
+      <c r="K49" s="25"/>
       <c r="L49" s="1">
         <v>46</v>
       </c>
-      <c r="N49" s="6" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>98</v>
       </c>
@@ -3570,7 +3548,7 @@
         <v>1</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E50" s="3">
         <f t="shared" si="7"/>
@@ -3587,15 +3565,12 @@
         <f t="shared" si="9"/>
         <v>115.48556430446209</v>
       </c>
-      <c r="K50" s="24"/>
+      <c r="K50" s="25"/>
       <c r="L50" s="1">
         <v>47</v>
       </c>
-      <c r="N50" s="6" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>99</v>
       </c>
@@ -3606,7 +3581,7 @@
         <v>1</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E51" s="3">
         <f t="shared" si="7"/>
@@ -3626,15 +3601,12 @@
       <c r="J51" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="K51" s="24"/>
+      <c r="K51" s="25"/>
       <c r="L51" s="1">
         <v>48</v>
       </c>
-      <c r="N51" s="6" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>94</v>
       </c>
@@ -3645,7 +3617,7 @@
         <v>1</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E52" s="3">
         <f t="shared" si="7"/>
@@ -3668,12 +3640,12 @@
       <c r="J52" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="K52" s="24"/>
+      <c r="K52" s="25"/>
       <c r="L52" s="1">
         <v>49</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>95</v>
       </c>
@@ -3684,7 +3656,7 @@
         <v>1</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E53" s="3">
         <f t="shared" si="7"/>
@@ -3707,12 +3679,12 @@
       <c r="J53" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="K53" s="24"/>
+      <c r="K53" s="25"/>
       <c r="L53" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>110</v>
       </c>
@@ -3745,12 +3717,12 @@
       <c r="J54" s="17" t="s">
         <v>324</v>
       </c>
-      <c r="K54" s="24"/>
+      <c r="K54" s="25"/>
       <c r="L54" s="1">
         <v>51</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>112</v>
       </c>
@@ -3783,12 +3755,12 @@
       <c r="J55" s="17" t="s">
         <v>344</v>
       </c>
-      <c r="K55" s="24"/>
+      <c r="K55" s="25"/>
       <c r="L55" s="1">
         <v>52</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>112</v>
       </c>
@@ -3821,12 +3793,12 @@
       <c r="J56" s="17" t="s">
         <v>350</v>
       </c>
-      <c r="K56" s="24"/>
+      <c r="K56" s="25"/>
       <c r="L56" s="1">
         <v>53</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>112</v>
       </c>
@@ -3859,12 +3831,12 @@
       <c r="J57" s="17" t="s">
         <v>347</v>
       </c>
-      <c r="K57" s="24"/>
+      <c r="K57" s="25"/>
       <c r="L57" s="1">
         <v>54</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>306</v>
       </c>
@@ -3892,19 +3864,19 @@
         <v>599.2913385826771</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="J58" s="17" t="s">
-        <v>385</v>
-      </c>
-      <c r="K58" s="24"/>
+        <v>356</v>
+      </c>
+      <c r="K58" s="25"/>
       <c r="L58" s="1">
         <v>55</v>
       </c>
     </row>
-    <row r="59" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="12" t="s">
-        <v>384</v>
+        <v>355</v>
       </c>
       <c r="B59" s="12">
         <v>9</v>
@@ -3913,7 +3885,7 @@
         <v>1</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>384</v>
+        <v>355</v>
       </c>
       <c r="E59" s="12">
         <v>313.05599999999998</v>
@@ -3922,25 +3894,25 @@
         <v>455.10700000000003</v>
       </c>
       <c r="G59" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="G59:G61" si="10">F59-E59</f>
         <v>142.05100000000004</v>
       </c>
       <c r="H59" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="H59:H61" si="11">G59/0.3048</f>
         <v>466.04658792650929</v>
       </c>
       <c r="I59" s="12" t="s">
-        <v>415</v>
+        <v>356</v>
       </c>
       <c r="J59" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="K59" s="25"/>
+        <v>354</v>
+      </c>
+      <c r="K59" s="26"/>
       <c r="L59" s="1">
         <v>56</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>0</v>
       </c>
@@ -3951,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>407</v>
+        <v>387</v>
       </c>
       <c r="E60" s="1">
         <v>-29.234999999999999</v>
@@ -3960,19 +3932,17 @@
         <v>0</v>
       </c>
       <c r="G60" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>29.234999999999999</v>
       </c>
       <c r="H60" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>95.915354330708652</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="K60" s="27" t="s">
-        <v>376</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="K60" s="24"/>
       <c r="L60" s="1">
         <v>57</v>
       </c>
@@ -3980,7 +3950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>0</v>
       </c>
@@ -3991,7 +3961,7 @@
         <v>0</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>411</v>
+        <v>392</v>
       </c>
       <c r="E61" s="1">
         <v>-3.2050000000000001</v>
@@ -4000,17 +3970,17 @@
         <v>0</v>
       </c>
       <c r="G61" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>3.2050000000000001</v>
       </c>
       <c r="H61" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>10.51509186351706</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="K61" s="28"/>
+        <v>391</v>
+      </c>
+      <c r="K61" s="24"/>
       <c r="L61" s="1">
         <v>58</v>
       </c>
@@ -4018,7 +3988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="str">
         <f>$A$5</f>
         <v>S01</v>
@@ -4043,14 +4013,16 @@
         <v>101.6</v>
       </c>
       <c r="G62" s="3">
-        <f>F62-E62</f>
+        <f>$G$5</f>
         <v>101.6</v>
       </c>
       <c r="H62" s="2">
-        <f>G62/0.3048</f>
+        <f>$H$5</f>
         <v>333.33333333333331</v>
       </c>
-      <c r="K62" s="28"/>
+      <c r="K62" s="28" t="s">
+        <v>364</v>
+      </c>
       <c r="L62" s="1">
         <v>59</v>
       </c>
@@ -4059,35 +4031,35 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B63" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C63" s="1">
         <v>0</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
       <c r="E63" s="3">
         <v>0</v>
       </c>
       <c r="F63" s="3">
-        <v>12.895</v>
+        <v>11.541</v>
       </c>
       <c r="G63" s="3">
         <f>F63-E63</f>
-        <v>12.895</v>
+        <v>11.541</v>
       </c>
       <c r="H63" s="2">
         <f>G63/0.3048</f>
-        <v>42.30643044619422</v>
+        <v>37.864173228346459</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="K63" s="28"/>
       <c r="L63" s="1">
@@ -4097,35 +4069,35 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B64" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C64" s="1">
         <v>0</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>413</v>
+        <v>389</v>
       </c>
       <c r="E64" s="3">
         <v>0</v>
       </c>
       <c r="F64" s="3">
-        <v>11.541</v>
+        <v>12.895</v>
       </c>
       <c r="G64" s="3">
         <f>F64-E64</f>
-        <v>11.541</v>
+        <v>12.895</v>
       </c>
       <c r="H64" s="2">
         <f>G64/0.3048</f>
-        <v>37.864173228346459</v>
+        <v>42.30643044619422</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>414</v>
+        <v>390</v>
       </c>
       <c r="K64" s="28"/>
       <c r="L64" s="1">
@@ -4148,7 +4120,7 @@
         <v>0</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>388</v>
+        <v>369</v>
       </c>
       <c r="E65" s="3">
         <f>$E$32</f>
@@ -4212,7 +4184,7 @@
         <v>63</v>
       </c>
       <c r="M66" s="1">
-        <f t="shared" ref="M66:M67" si="10">$L$32</f>
+        <f t="shared" ref="M66:M67" si="12">$L$32</f>
         <v>29</v>
       </c>
     </row>
@@ -4253,7 +4225,7 @@
         <v>64</v>
       </c>
       <c r="M67" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>29</v>
       </c>
     </row>
@@ -4270,7 +4242,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>389</v>
+        <v>365</v>
       </c>
       <c r="E68" s="3">
         <f>$E$33</f>
@@ -4310,7 +4282,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="E69" s="3">
         <f>$E$33</f>
@@ -4333,7 +4305,7 @@
         <v>66</v>
       </c>
       <c r="M69" s="1">
-        <f t="shared" ref="M69:M70" si="11">$L$33</f>
+        <f t="shared" ref="M69:M70" si="13">$L$33</f>
         <v>30</v>
       </c>
     </row>
@@ -4350,7 +4322,7 @@
         <v>0</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>391</v>
+        <v>372</v>
       </c>
       <c r="E70" s="3">
         <f>$E$33</f>
@@ -4373,7 +4345,7 @@
         <v>67</v>
       </c>
       <c r="M70" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>30</v>
       </c>
     </row>
@@ -4390,7 +4362,7 @@
         <v>0</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>389</v>
+        <v>365</v>
       </c>
       <c r="E71" s="3">
         <f>$E$34</f>
@@ -4430,7 +4402,7 @@
         <v>0</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>392</v>
+        <v>371</v>
       </c>
       <c r="E72" s="3">
         <f>$E$34</f>
@@ -4470,7 +4442,7 @@
         <v>0</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>393</v>
+        <v>366</v>
       </c>
       <c r="E73" s="3">
         <f>$E$34</f>
@@ -4510,7 +4482,7 @@
         <v>1</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>394</v>
+        <v>374</v>
       </c>
       <c r="E74" s="3">
         <v>2.512</v>
@@ -4548,7 +4520,7 @@
         <v>1</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>395</v>
+        <v>367</v>
       </c>
       <c r="E75" s="3">
         <v>2.512</v>
@@ -4586,7 +4558,7 @@
         <v>1</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>396</v>
+        <v>368</v>
       </c>
       <c r="E76" s="13">
         <v>2.512</v>
@@ -4604,7 +4576,7 @@
       </c>
       <c r="I76" s="12"/>
       <c r="J76" s="12" t="s">
-        <v>397</v>
+        <v>373</v>
       </c>
       <c r="K76" s="29"/>
       <c r="L76" s="1">
@@ -4625,17 +4597,20 @@
         <v>1</v>
       </c>
       <c r="B79" s="20" t="s">
-        <v>359</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="K4:K34"/>
     <mergeCell ref="K35:K59"/>
-    <mergeCell ref="K60:K76"/>
+    <mergeCell ref="K62:K76"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
   <pageSetup scale="61" orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="G62:H62 G75" formula="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -4653,7 +4628,8 @@
     <col min="4" max="4" width="28.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" style="6" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="17.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -4675,7 +4651,7 @@
       <c r="C1" s="10"/>
       <c r="F1" s="7"/>
       <c r="G1" s="3"/>
-      <c r="H1" s="2"/>
+      <c r="H1" s="3"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -4685,7 +4661,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="7"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="2"/>
+      <c r="H2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
@@ -4709,7 +4685,7 @@
       <c r="G3" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="13" t="s">
         <v>26</v>
       </c>
       <c r="I3" s="12" t="s">
@@ -4731,7 +4707,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>64</v>
+        <v>381</v>
       </c>
       <c r="E4" s="3">
         <v>2017.911482</v>
@@ -4743,7 +4719,7 @@
         <f>F4-E4</f>
         <v>17.123648000000003</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="3">
         <f>G4/0.3048</f>
         <v>56.179947506561689</v>
       </c>
@@ -4753,7 +4729,7 @@
       <c r="J4" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="K4" s="24" t="s">
+      <c r="K4" s="25" t="s">
         <v>28</v>
       </c>
       <c r="L4" s="1">
@@ -4785,17 +4761,17 @@
         <f t="shared" ref="G5:G14" si="0">F5-E5</f>
         <v>98.564869999999928</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="3">
         <f t="shared" ref="H5:H14" si="1">G5/0.3048</f>
         <v>323.37555774278189</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="K5" s="24"/>
+      <c r="K5" s="25"/>
       <c r="L5" s="1">
         <v>2</v>
       </c>
@@ -4811,7 +4787,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E6" s="3">
         <f t="shared" ref="E6:E14" si="2">F5</f>
@@ -4825,7 +4801,7 @@
         <f t="shared" si="0"/>
         <v>101.59999999999991</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="3">
         <f t="shared" si="1"/>
         <v>333.33333333333303</v>
       </c>
@@ -4835,7 +4811,7 @@
       <c r="J6" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="K6" s="24"/>
+      <c r="K6" s="25"/>
       <c r="L6" s="1">
         <v>3</v>
       </c>
@@ -4851,7 +4827,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E7" s="3">
         <f t="shared" si="2"/>
@@ -4865,7 +4841,7 @@
         <f t="shared" si="0"/>
         <v>101.59999999999991</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="3">
         <f t="shared" si="1"/>
         <v>333.33333333333303</v>
       </c>
@@ -4875,7 +4851,7 @@
       <c r="J7" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="K7" s="24"/>
+      <c r="K7" s="25"/>
       <c r="L7" s="1">
         <v>4</v>
       </c>
@@ -4905,7 +4881,7 @@
         <f t="shared" si="0"/>
         <v>101.59999999999991</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="3">
         <f t="shared" si="1"/>
         <v>333.33333333333303</v>
       </c>
@@ -4913,9 +4889,9 @@
         <v>151</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="K8" s="24"/>
+        <v>314</v>
+      </c>
+      <c r="K8" s="25"/>
       <c r="L8" s="1">
         <v>5</v>
       </c>
@@ -4931,7 +4907,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E9" s="3">
         <f t="shared" si="2"/>
@@ -4945,7 +4921,7 @@
         <f t="shared" si="0"/>
         <v>101.60000000000036</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="3">
         <f t="shared" si="1"/>
         <v>333.33333333333451</v>
       </c>
@@ -4955,7 +4931,7 @@
       <c r="J9" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="K9" s="24"/>
+      <c r="K9" s="25"/>
       <c r="L9" s="1">
         <v>6</v>
       </c>
@@ -4971,7 +4947,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E10" s="3">
         <f t="shared" si="2"/>
@@ -4985,7 +4961,7 @@
         <f t="shared" si="0"/>
         <v>101.59999999999991</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="3">
         <f t="shared" si="1"/>
         <v>333.33333333333303</v>
       </c>
@@ -4995,7 +4971,7 @@
       <c r="J10" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K10" s="24"/>
+      <c r="K10" s="25"/>
       <c r="L10" s="1">
         <v>7</v>
       </c>
@@ -5011,7 +4987,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E11" s="3">
         <f t="shared" si="2"/>
@@ -5025,7 +5001,7 @@
         <f t="shared" si="0"/>
         <v>101.59999999999991</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="3">
         <f t="shared" si="1"/>
         <v>333.33333333333303</v>
       </c>
@@ -5035,7 +5011,7 @@
       <c r="J11" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="K11" s="24"/>
+      <c r="K11" s="25"/>
       <c r="L11" s="1">
         <v>8</v>
       </c>
@@ -5051,7 +5027,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E12" s="3">
         <f t="shared" si="2"/>
@@ -5065,7 +5041,7 @@
         <f t="shared" si="0"/>
         <v>101.59999999999991</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="3">
         <f t="shared" si="1"/>
         <v>333.33333333333303</v>
       </c>
@@ -5075,7 +5051,7 @@
       <c r="J12" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="K12" s="24"/>
+      <c r="K12" s="25"/>
       <c r="L12" s="1">
         <v>9</v>
       </c>
@@ -5091,7 +5067,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E13" s="3">
         <f t="shared" si="2"/>
@@ -5105,7 +5081,7 @@
         <f t="shared" si="0"/>
         <v>101.59999999999991</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="3">
         <f t="shared" si="1"/>
         <v>333.33333333333303</v>
       </c>
@@ -5115,7 +5091,7 @@
       <c r="J13" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="K13" s="24"/>
+      <c r="K13" s="25"/>
       <c r="L13" s="1">
         <v>10</v>
       </c>
@@ -5144,7 +5120,7 @@
         <f t="shared" si="0"/>
         <v>104.11200000000053</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="13">
         <f t="shared" si="1"/>
         <v>341.57480314960804</v>
       </c>
@@ -5154,7 +5130,7 @@
       <c r="J14" s="18" t="s">
         <v>326</v>
       </c>
-      <c r="K14" s="25"/>
+      <c r="K14" s="26"/>
       <c r="L14" s="1">
         <v>11</v>
       </c>
@@ -5170,7 +5146,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>313</v>
+        <v>357</v>
       </c>
       <c r="E15" s="3">
         <v>2.512</v>
@@ -5182,7 +5158,7 @@
         <f t="shared" ref="G15:G27" si="3">F15-E15</f>
         <v>173.50899999999999</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="3">
         <f t="shared" ref="H15:H27" si="4">G15/0.3048</f>
         <v>569.25524934383191</v>
       </c>
@@ -5190,10 +5166,10 @@
         <v>327</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="K15" s="26" t="s">
-        <v>29</v>
+        <v>358</v>
+      </c>
+      <c r="K15" s="27" t="s">
+        <v>379</v>
       </c>
       <c r="L15" s="1">
         <v>12</v>
@@ -5210,7 +5186,7 @@
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E16" s="3">
         <f>F15</f>
@@ -5223,19 +5199,19 @@
         <f t="shared" si="3"/>
         <v>27.509000000000015</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="3">
         <f t="shared" si="4"/>
         <v>90.252624671916053</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="K16" s="24"/>
+      <c r="K16" s="25"/>
       <c r="L16" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>69</v>
       </c>
@@ -5246,7 +5222,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E17" s="3">
         <f t="shared" ref="E17:E33" si="5">F16</f>
@@ -5259,16 +5235,16 @@
         <f t="shared" si="3"/>
         <v>27.749300000000005</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17" s="3">
         <f t="shared" si="4"/>
         <v>91.041010498687683</v>
       </c>
-      <c r="K17" s="24"/>
+      <c r="K17" s="25"/>
       <c r="L17" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>70</v>
       </c>
@@ -5279,7 +5255,7 @@
         <v>1</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E18" s="3">
         <f t="shared" si="5"/>
@@ -5292,16 +5268,16 @@
         <f t="shared" si="3"/>
         <v>29.200700000000012</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18" s="3">
         <f t="shared" si="4"/>
         <v>95.802821522309742</v>
       </c>
-      <c r="K18" s="24"/>
+      <c r="K18" s="25"/>
       <c r="L18" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>71</v>
       </c>
@@ -5312,7 +5288,7 @@
         <v>1</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E19" s="3">
         <f t="shared" si="5"/>
@@ -5325,16 +5301,16 @@
         <f t="shared" si="3"/>
         <v>26.279999999999973</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19" s="3">
         <f t="shared" si="4"/>
         <v>86.220472440944789</v>
       </c>
-      <c r="K19" s="24"/>
+      <c r="K19" s="25"/>
       <c r="L19" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>72</v>
       </c>
@@ -5345,7 +5321,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E20" s="3">
         <f t="shared" si="5"/>
@@ -5358,16 +5334,16 @@
         <f t="shared" si="3"/>
         <v>27.769999999999982</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H20" s="3">
         <f t="shared" si="4"/>
         <v>91.108923884514368</v>
       </c>
-      <c r="K20" s="24"/>
+      <c r="K20" s="25"/>
       <c r="L20" s="1">
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>73</v>
       </c>
@@ -5378,7 +5354,7 @@
         <v>1</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E21" s="3">
         <f t="shared" si="5"/>
@@ -5391,16 +5367,16 @@
         <f t="shared" si="3"/>
         <v>27.740000000000009</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H21" s="3">
         <f t="shared" si="4"/>
         <v>91.010498687664068</v>
       </c>
-      <c r="K21" s="24"/>
+      <c r="K21" s="25"/>
       <c r="L21" s="1">
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>74</v>
       </c>
@@ -5411,7 +5387,7 @@
         <v>1</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E22" s="3">
         <f t="shared" si="5"/>
@@ -5424,16 +5400,16 @@
         <f t="shared" si="3"/>
         <v>29.150000000000034</v>
       </c>
-      <c r="H22" s="2">
+      <c r="H22" s="3">
         <f t="shared" si="4"/>
         <v>95.636482939632657</v>
       </c>
-      <c r="K22" s="24"/>
+      <c r="K22" s="25"/>
       <c r="L22" s="1">
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>75</v>
       </c>
@@ -5444,7 +5420,7 @@
         <v>1</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E23" s="3">
         <f t="shared" si="5"/>
@@ -5457,16 +5433,16 @@
         <f t="shared" si="3"/>
         <v>26.339999999999975</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H23" s="3">
         <f t="shared" si="4"/>
         <v>86.417322834645589</v>
       </c>
-      <c r="K23" s="24"/>
+      <c r="K23" s="25"/>
       <c r="L23" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>76</v>
       </c>
@@ -5477,7 +5453,7 @@
         <v>1</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E24" s="3">
         <f t="shared" si="5"/>
@@ -5490,16 +5466,16 @@
         <f t="shared" si="3"/>
         <v>27.769999999999982</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H24" s="3">
         <f t="shared" si="4"/>
         <v>91.108923884514368</v>
       </c>
-      <c r="K24" s="24"/>
+      <c r="K24" s="25"/>
       <c r="L24" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>77</v>
       </c>
@@ -5510,7 +5486,7 @@
         <v>1</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E25" s="3">
         <f t="shared" si="5"/>
@@ -5523,16 +5499,16 @@
         <f t="shared" si="3"/>
         <v>27.75</v>
       </c>
-      <c r="H25" s="2">
+      <c r="H25" s="3">
         <f t="shared" si="4"/>
         <v>91.043307086614163</v>
       </c>
-      <c r="K25" s="24"/>
+      <c r="K25" s="25"/>
       <c r="L25" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>78</v>
       </c>
@@ -5543,7 +5519,7 @@
         <v>1</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E26" s="3">
         <f t="shared" si="5"/>
@@ -5556,16 +5532,16 @@
         <f t="shared" si="3"/>
         <v>27.75</v>
       </c>
-      <c r="H26" s="2">
+      <c r="H26" s="3">
         <f t="shared" si="4"/>
         <v>91.043307086614163</v>
       </c>
-      <c r="K26" s="24"/>
+      <c r="K26" s="25"/>
       <c r="L26" s="1">
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>79</v>
       </c>
@@ -5576,7 +5552,7 @@
         <v>1</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E27" s="3">
         <f t="shared" si="5"/>
@@ -5589,19 +5565,19 @@
         <f t="shared" si="3"/>
         <v>33.710001000000034</v>
       </c>
-      <c r="H27" s="2">
+      <c r="H27" s="3">
         <f t="shared" si="4"/>
         <v>110.59711614173239</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="K27" s="24"/>
+      <c r="K27" s="25"/>
       <c r="L27" s="1">
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>100</v>
       </c>
@@ -5612,7 +5588,7 @@
         <v>1</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>357</v>
+        <v>27</v>
       </c>
       <c r="E28" s="3">
         <f t="shared" si="5"/>
@@ -5632,15 +5608,12 @@
       <c r="I28" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="K28" s="24"/>
+      <c r="K28" s="25"/>
       <c r="L28" s="1">
         <v>25</v>
       </c>
-      <c r="N28" s="3" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>101</v>
       </c>
@@ -5668,15 +5641,12 @@
         <f>G29/0.3048</f>
         <v>118.48425196850404</v>
       </c>
-      <c r="K29" s="24"/>
+      <c r="K29" s="25"/>
       <c r="L29" s="1">
         <v>26</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>102</v>
       </c>
@@ -5704,15 +5674,12 @@
         <f>G30/0.3048</f>
         <v>118.48425196850404</v>
       </c>
-      <c r="K30" s="24"/>
+      <c r="K30" s="25"/>
       <c r="L30" s="1">
         <v>27</v>
       </c>
-      <c r="N30" s="3" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>103</v>
       </c>
@@ -5743,15 +5710,12 @@
       <c r="J31" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="K31" s="24"/>
+      <c r="K31" s="25"/>
       <c r="L31" s="1">
         <v>28</v>
       </c>
-      <c r="N31" s="3" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>80</v>
       </c>
@@ -5775,7 +5739,7 @@
         <f t="shared" si="6"/>
         <v>15.923506999999972</v>
       </c>
-      <c r="H32" s="2">
+      <c r="H32" s="3">
         <f t="shared" ref="H32" si="7">G32/0.3048</f>
         <v>52.24247703412064</v>
       </c>
@@ -5785,7 +5749,7 @@
       <c r="J32" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="K32" s="24"/>
+      <c r="K32" s="25"/>
       <c r="L32" s="1">
         <v>29</v>
       </c>
@@ -5801,7 +5765,7 @@
         <v>1</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E33" s="3">
         <f t="shared" si="5"/>
@@ -5814,7 +5778,7 @@
         <f t="shared" si="6"/>
         <v>31.065000000000055</v>
       </c>
-      <c r="H33" s="2">
+      <c r="H33" s="3">
         <f>G33/0.3048</f>
         <v>101.91929133858285</v>
       </c>
@@ -5824,7 +5788,7 @@
       <c r="J33" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="K33" s="24"/>
+      <c r="K33" s="25"/>
       <c r="L33" s="1">
         <v>30</v>
       </c>
@@ -5852,7 +5816,7 @@
         <f t="shared" si="6"/>
         <v>27.665869999999927</v>
       </c>
-      <c r="H34" s="2">
+      <c r="H34" s="3">
         <f t="shared" ref="H34" si="8">G34/0.3048</f>
         <v>90.767290026246471</v>
       </c>
@@ -5862,7 +5826,7 @@
       <c r="J34" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="K34" s="24"/>
+      <c r="K34" s="25"/>
       <c r="L34" s="1">
         <v>31</v>
       </c>
@@ -5890,7 +5854,7 @@
         <f t="shared" ref="G35" si="9">F35-E35</f>
         <v>58.533928999999944</v>
       </c>
-      <c r="H35" s="2">
+      <c r="H35" s="3">
         <f t="shared" ref="H35" si="10">G35/0.3048</f>
         <v>192.04044947506543</v>
       </c>
@@ -5900,7 +5864,7 @@
       <c r="J35" s="17" t="s">
         <v>338</v>
       </c>
-      <c r="K35" s="24"/>
+      <c r="K35" s="25"/>
       <c r="L35" s="1">
         <v>32</v>
       </c>
@@ -5928,7 +5892,7 @@
         <f t="shared" si="6"/>
         <v>18.360869999999977</v>
       </c>
-      <c r="H36" s="14">
+      <c r="H36" s="13">
         <f t="shared" ref="H36:H37" si="11">G36/0.3048</f>
         <v>60.239074803149528</v>
       </c>
@@ -5938,7 +5902,7 @@
       <c r="J36" s="18" t="s">
         <v>341</v>
       </c>
-      <c r="K36" s="25"/>
+      <c r="K36" s="26"/>
       <c r="L36" s="1">
         <v>33</v>
       </c>
@@ -5954,7 +5918,7 @@
         <v>1</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="E37" s="3">
         <v>10.456</v>
@@ -5971,13 +5935,13 @@
         <v>391.06299212598418</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="K37" s="26" t="s">
-        <v>376</v>
+        <v>377</v>
+      </c>
+      <c r="K37" s="27" t="s">
+        <v>364</v>
       </c>
       <c r="L37" s="1">
         <v>34</v>
@@ -5997,7 +5961,7 @@
         <v>0</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="E38" s="3">
         <v>2018.712</v>
@@ -6014,12 +5978,12 @@
         <v>0.86942257217880592</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="K38" s="24"/>
+        <v>380</v>
+      </c>
+      <c r="K38" s="25"/>
       <c r="L38" s="1">
         <v>35</v>
       </c>
@@ -6038,7 +6002,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E39" s="13">
         <v>2031.991</v>
@@ -6055,12 +6019,12 @@
         <v>15.695538057743127</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>382</v>
-      </c>
-      <c r="K39" s="25"/>
+        <v>386</v>
+      </c>
+      <c r="K39" s="26"/>
       <c r="L39" s="1">
         <v>36</v>
       </c>
@@ -6083,7 +6047,7 @@
         <v>1</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>359</v>
+        <v>315</v>
       </c>
       <c r="K42" s="11"/>
     </row>
@@ -6160,8 +6124,7 @@
     <col min="4" max="5" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="3"/>
     <col min="7" max="7" width="9.140625" style="2"/>
-    <col min="8" max="8" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6186,11 +6149,11 @@
       <c r="G1" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="14" t="s">
-        <v>400</v>
-      </c>
-      <c r="I1" s="14" t="s">
-        <v>401</v>
+      <c r="H1" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -6201,7 +6164,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D2" s="3">
         <v>517.54</v>
@@ -6217,8 +6180,8 @@
         <f>F2/0.3048</f>
         <v>8.0265485564305603</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>399</v>
+      <c r="I2" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -6229,7 +6192,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>360</v>
+        <v>401</v>
       </c>
       <c r="D3" s="3">
         <v>519.986492</v>
@@ -6257,7 +6220,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>361</v>
+        <v>402</v>
       </c>
       <c r="D4" s="3">
         <v>524.38649199999998</v>
@@ -6285,7 +6248,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>362</v>
+        <v>403</v>
       </c>
       <c r="D5" s="3">
         <v>528.78649199999995</v>
@@ -6313,7 +6276,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>363</v>
+        <v>404</v>
       </c>
       <c r="D6" s="3">
         <v>533.18649200000004</v>
@@ -6341,7 +6304,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>364</v>
+        <v>405</v>
       </c>
       <c r="D7" s="3">
         <v>537.58649200000002</v>
@@ -6369,7 +6332,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>365</v>
+        <v>406</v>
       </c>
       <c r="D8" s="3">
         <v>541.986492</v>
@@ -6397,7 +6360,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>366</v>
+        <v>407</v>
       </c>
       <c r="D9" s="3">
         <v>546.38649199999998</v>
@@ -6425,7 +6388,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>367</v>
+        <v>408</v>
       </c>
       <c r="D10" s="3">
         <v>550.78649199999995</v>
@@ -6453,7 +6416,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>368</v>
+        <v>409</v>
       </c>
       <c r="D11" s="3">
         <v>555.18649200000004</v>
@@ -6750,7 +6713,7 @@
         <v>14.435695538057667</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>402</v>
+        <v>353</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -7116,8 +7079,8 @@
       <c r="H34" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="I34" s="1" t="s">
-        <v>403</v>
+      <c r="I34" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -7178,18 +7141,18 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7214,87 +7177,84 @@
       <c r="G1" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="14" t="s">
-        <v>400</v>
-      </c>
-      <c r="I1" s="14" t="s">
-        <v>401</v>
+      <c r="H1" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>369</v>
+        <v>228</v>
       </c>
       <c r="B2" s="1">
         <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>369</v>
+        <v>224</v>
       </c>
       <c r="D2" s="3">
         <v>514.74000100000001</v>
       </c>
       <c r="E2" s="3">
-        <v>515.09498499999995</v>
+        <v>519.10765100000003</v>
       </c>
       <c r="F2" s="3">
-        <f>E2-D2</f>
-        <v>0.3549839999999449</v>
+        <f t="shared" ref="F2:F4" si="0">E2-D2</f>
+        <v>4.367650000000026</v>
       </c>
       <c r="G2" s="2">
-        <f>F2/0.3048</f>
-        <v>1.1646456692911578</v>
+        <f t="shared" ref="G2:G4" si="1">F2/0.3048</f>
+        <v>14.329560367454153</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="I2" s="1"/>
+        <v>361</v>
+      </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B3" s="1">
         <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D3" s="3">
-        <f>E2</f>
-        <v>515.09498499999995</v>
+        <v>519.10765100000003</v>
       </c>
       <c r="E3" s="3">
-        <v>519.10765100000003</v>
+        <v>523.120318</v>
       </c>
       <c r="F3" s="3">
-        <f t="shared" ref="F3:F5" si="0">E3-D3</f>
-        <v>4.0126660000000811</v>
+        <f t="shared" si="0"/>
+        <v>4.0126669999999649</v>
       </c>
       <c r="G3" s="2">
-        <f t="shared" ref="G3:G5" si="1">F3/0.3048</f>
-        <v>13.164914698162995</v>
+        <f t="shared" si="1"/>
+        <v>13.164917979002508</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="I3" s="1"/>
+        <v>187</v>
+      </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B4" s="1">
         <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D4" s="3">
-        <v>519.10765100000003</v>
+        <v>523.120318</v>
       </c>
       <c r="E4" s="3">
-        <v>523.120318</v>
+        <v>527.13298499999996</v>
       </c>
       <c r="F4" s="3">
         <f t="shared" si="0"/>
@@ -7307,168 +7267,162 @@
       <c r="H4" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I4" s="1"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B5" s="1">
         <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>226</v>
+        <v>189</v>
       </c>
       <c r="D5" s="3">
-        <v>523.120318</v>
+        <v>527.13298499999996</v>
       </c>
       <c r="E5" s="3">
-        <v>527.13298499999996</v>
+        <v>531.14565100000004</v>
       </c>
       <c r="F5" s="3">
-        <f t="shared" si="0"/>
-        <v>4.0126669999999649</v>
+        <f>E5-D5</f>
+        <v>4.0126660000000811</v>
       </c>
       <c r="G5" s="2">
-        <f t="shared" si="1"/>
-        <v>13.164917979002508</v>
+        <f>F5/0.3048</f>
+        <v>13.164914698162995</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I5" s="1"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B6" s="1">
         <v>10</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D6" s="3">
-        <v>527.13298499999996</v>
+        <v>531.14565100000004</v>
       </c>
       <c r="E6" s="3">
-        <v>531.14565100000004</v>
+        <v>535.15831800000001</v>
       </c>
       <c r="F6" s="3">
-        <f>E6-D6</f>
-        <v>4.0126660000000811</v>
+        <f t="shared" ref="F6:F39" si="2">E6-D6</f>
+        <v>4.0126669999999649</v>
       </c>
       <c r="G6" s="2">
-        <f>F6/0.3048</f>
-        <v>13.164914698162995</v>
+        <f t="shared" ref="G6:G39" si="3">F6/0.3048</f>
+        <v>13.164917979002508</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I6" s="1"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B7" s="1">
         <v>10</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D7" s="3">
-        <v>531.14565100000004</v>
+        <v>535.15831800000001</v>
       </c>
       <c r="E7" s="3">
-        <v>535.15831800000001</v>
+        <v>539.17098499999997</v>
       </c>
       <c r="F7" s="3">
-        <f t="shared" ref="F7:F40" si="2">E7-D7</f>
+        <f t="shared" si="2"/>
         <v>4.0126669999999649</v>
       </c>
       <c r="G7" s="2">
-        <f t="shared" ref="G7:G40" si="3">F7/0.3048</f>
+        <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I7" s="1"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B8" s="1">
         <v>10</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D8" s="3">
-        <v>535.15831800000001</v>
+        <v>539.17098499999997</v>
       </c>
       <c r="E8" s="3">
-        <v>539.17098499999997</v>
+        <v>543.18365100000005</v>
       </c>
       <c r="F8" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126669999999649</v>
+        <v>4.0126660000000811</v>
       </c>
       <c r="G8" s="2">
         <f t="shared" si="3"/>
-        <v>13.164917979002508</v>
+        <v>13.164914698162995</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I8" s="1"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B9" s="1">
         <v>10</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D9" s="3">
-        <v>539.17098499999997</v>
+        <v>543.18365100000005</v>
       </c>
       <c r="E9" s="3">
-        <v>543.18365100000005</v>
+        <v>547.19631800000002</v>
       </c>
       <c r="F9" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126660000000811</v>
+        <v>4.0126669999999649</v>
       </c>
       <c r="G9" s="2">
         <f t="shared" si="3"/>
-        <v>13.164914698162995</v>
+        <v>13.164917979002508</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I9" s="1"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B10" s="1">
         <v>10</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D10" s="3">
-        <v>543.18365100000005</v>
+        <v>547.19631800000002</v>
       </c>
       <c r="E10" s="3">
-        <v>547.19631800000002</v>
+        <v>551.20898499999998</v>
       </c>
       <c r="F10" s="3">
         <f t="shared" si="2"/>
@@ -7479,605 +7433,584 @@
         <v>13.164917979002508</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="I10" s="1"/>
+        <v>351</v>
+      </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B11" s="1">
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D11" s="3">
-        <v>547.19631800000002</v>
+        <v>551.20898499999998</v>
       </c>
       <c r="E11" s="3">
-        <v>551.20898499999998</v>
+        <v>555.22165099999995</v>
       </c>
       <c r="F11" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126669999999649</v>
+        <v>4.0126659999999674</v>
       </c>
       <c r="G11" s="2">
         <f t="shared" si="3"/>
-        <v>13.164917979002508</v>
+        <v>13.164914698162622</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="I11" s="1"/>
+        <v>187</v>
+      </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B12" s="1">
         <v>10</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D12" s="3">
-        <v>551.20898499999998</v>
+        <v>555.22165099999995</v>
       </c>
       <c r="E12" s="3">
-        <v>555.22165099999995</v>
+        <v>559.23431800000003</v>
       </c>
       <c r="F12" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126659999999674</v>
+        <v>4.0126670000000786</v>
       </c>
       <c r="G12" s="2">
         <f t="shared" si="3"/>
-        <v>13.164914698162622</v>
+        <v>13.164917979002881</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I12" s="1"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B13" s="1">
         <v>10</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D13" s="3">
-        <v>555.22165099999995</v>
+        <v>559.23431800000003</v>
       </c>
       <c r="E13" s="3">
-        <v>559.23431800000003</v>
+        <v>563.246985</v>
       </c>
       <c r="F13" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126670000000786</v>
+        <v>4.0126669999999649</v>
       </c>
       <c r="G13" s="2">
         <f t="shared" si="3"/>
-        <v>13.164917979002881</v>
+        <v>13.164917979002508</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I13" s="1"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B14" s="1">
         <v>10</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D14" s="3">
-        <v>559.23431800000003</v>
+        <v>563.246985</v>
       </c>
       <c r="E14" s="3">
-        <v>563.246985</v>
+        <v>567.25965099999996</v>
       </c>
       <c r="F14" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126669999999649</v>
+        <v>4.0126659999999674</v>
       </c>
       <c r="G14" s="2">
         <f t="shared" si="3"/>
-        <v>13.164917979002508</v>
+        <v>13.164914698162622</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B15" s="1">
         <v>10</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D15" s="3">
-        <v>563.246985</v>
+        <v>567.25965099999996</v>
       </c>
       <c r="E15" s="3">
-        <v>567.25965099999996</v>
+        <v>571.27231800000004</v>
       </c>
       <c r="F15" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126659999999674</v>
+        <v>4.0126670000000786</v>
       </c>
       <c r="G15" s="2">
         <f t="shared" si="3"/>
-        <v>13.164914698162622</v>
+        <v>13.164917979002881</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I15" s="1"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B16" s="1">
         <v>10</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D16" s="3">
-        <v>567.25965099999996</v>
+        <v>571.27231800000004</v>
       </c>
       <c r="E16" s="3">
-        <v>571.27231800000004</v>
+        <v>575.28498500000001</v>
       </c>
       <c r="F16" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126670000000786</v>
+        <v>4.0126669999999649</v>
       </c>
       <c r="G16" s="2">
         <f t="shared" si="3"/>
-        <v>13.164917979002881</v>
+        <v>13.164917979002508</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I16" s="1"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B17" s="1">
         <v>10</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D17" s="3">
-        <v>571.27231800000004</v>
+        <v>575.28498500000001</v>
       </c>
       <c r="E17" s="3">
-        <v>575.28498500000001</v>
+        <v>579.29765099999997</v>
       </c>
       <c r="F17" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126669999999649</v>
+        <v>4.0126659999999674</v>
       </c>
       <c r="G17" s="2">
         <f t="shared" si="3"/>
-        <v>13.164917979002508</v>
+        <v>13.164914698162622</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="I17" s="1"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B18" s="1">
         <v>10</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D18" s="3">
-        <v>575.28498500000001</v>
+        <v>579.29765099999997</v>
       </c>
       <c r="E18" s="3">
-        <v>579.29765099999997</v>
+        <v>583.31031800000005</v>
       </c>
       <c r="F18" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126659999999674</v>
+        <v>4.0126670000000786</v>
       </c>
       <c r="G18" s="2">
         <f t="shared" si="3"/>
-        <v>13.164914698162622</v>
+        <v>13.164917979002881</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="I18" s="1"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B19" s="1">
         <v>10</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D19" s="3">
-        <v>579.29765099999997</v>
+        <v>583.31031800000005</v>
       </c>
       <c r="E19" s="3">
-        <v>583.31031800000005</v>
+        <v>587.32298500000002</v>
       </c>
       <c r="F19" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126670000000786</v>
+        <v>4.0126669999999649</v>
       </c>
       <c r="G19" s="2">
         <f t="shared" si="3"/>
-        <v>13.164917979002881</v>
+        <v>13.164917979002508</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I19" s="1"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B20" s="1">
         <v>10</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D20" s="3">
-        <v>583.31031800000005</v>
+        <v>587.32298500000002</v>
       </c>
       <c r="E20" s="3">
-        <v>587.32298500000002</v>
+        <v>591.33565099999998</v>
       </c>
       <c r="F20" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126669999999649</v>
+        <v>4.0126659999999674</v>
       </c>
       <c r="G20" s="2">
         <f t="shared" si="3"/>
-        <v>13.164917979002508</v>
+        <v>13.164914698162622</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I20" s="1"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B21" s="1">
         <v>10</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D21" s="3">
-        <v>587.32298500000002</v>
+        <v>591.33565099999998</v>
       </c>
       <c r="E21" s="3">
-        <v>591.33565099999998</v>
+        <v>595.34831799999995</v>
       </c>
       <c r="F21" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126659999999674</v>
+        <v>4.0126669999999649</v>
       </c>
       <c r="G21" s="2">
         <f t="shared" si="3"/>
-        <v>13.164914698162622</v>
+        <v>13.164917979002508</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I21" s="1"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B22" s="1">
         <v>10</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D22" s="3">
-        <v>591.33565099999998</v>
+        <v>595.34831799999995</v>
       </c>
       <c r="E22" s="3">
-        <v>595.34831799999995</v>
+        <v>599.36098500000003</v>
       </c>
       <c r="F22" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126669999999649</v>
+        <v>4.0126670000000786</v>
       </c>
       <c r="G22" s="2">
         <f t="shared" si="3"/>
-        <v>13.164917979002508</v>
+        <v>13.164917979002881</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I22" s="1"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B23" s="1">
         <v>10</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D23" s="3">
-        <v>595.34831799999995</v>
+        <v>599.36098500000003</v>
       </c>
       <c r="E23" s="3">
-        <v>599.36098500000003</v>
+        <v>603.373651</v>
       </c>
       <c r="F23" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126670000000786</v>
+        <v>4.0126659999999674</v>
       </c>
       <c r="G23" s="2">
         <f t="shared" si="3"/>
-        <v>13.164917979002881</v>
+        <v>13.164914698162622</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I23" s="1"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B24" s="1">
         <v>10</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D24" s="3">
-        <v>599.36098500000003</v>
+        <v>603.373651</v>
       </c>
       <c r="E24" s="3">
-        <v>603.373651</v>
+        <v>607.38631799999996</v>
       </c>
       <c r="F24" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126659999999674</v>
+        <v>4.0126669999999649</v>
       </c>
       <c r="G24" s="2">
         <f t="shared" si="3"/>
-        <v>13.164914698162622</v>
+        <v>13.164917979002508</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I24" s="1"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B25" s="1">
         <v>10</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D25" s="3">
-        <v>603.373651</v>
+        <v>607.38631799999996</v>
       </c>
       <c r="E25" s="3">
-        <v>607.38631799999996</v>
+        <v>611.39898500000004</v>
       </c>
       <c r="F25" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126669999999649</v>
+        <v>4.0126670000000786</v>
       </c>
       <c r="G25" s="2">
         <f t="shared" si="3"/>
-        <v>13.164917979002508</v>
+        <v>13.164917979002881</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I25" s="1"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B26" s="1">
         <v>10</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D26" s="3">
-        <v>607.38631799999996</v>
+        <v>611.39898500000004</v>
       </c>
       <c r="E26" s="3">
-        <v>611.39898500000004</v>
+        <v>615.41165100000001</v>
       </c>
       <c r="F26" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126670000000786</v>
+        <v>4.0126659999999674</v>
       </c>
       <c r="G26" s="2">
         <f t="shared" si="3"/>
-        <v>13.164917979002881</v>
+        <v>13.164914698162622</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I26" s="1"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B27" s="1">
         <v>10</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D27" s="3">
-        <v>611.39898500000004</v>
+        <v>615.41165100000001</v>
       </c>
       <c r="E27" s="3">
-        <v>615.41165100000001</v>
+        <v>619.42431799999997</v>
       </c>
       <c r="F27" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126659999999674</v>
+        <v>4.0126669999999649</v>
       </c>
       <c r="G27" s="2">
         <f t="shared" si="3"/>
-        <v>13.164914698162622</v>
+        <v>13.164917979002508</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I27" s="1"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B28" s="1">
         <v>10</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D28" s="3">
-        <v>615.41165100000001</v>
+        <v>619.42431799999997</v>
       </c>
       <c r="E28" s="3">
-        <v>619.42431799999997</v>
+        <v>623.43698500000005</v>
       </c>
       <c r="F28" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126669999999649</v>
+        <v>4.0126670000000786</v>
       </c>
       <c r="G28" s="2">
         <f t="shared" si="3"/>
-        <v>13.164917979002508</v>
+        <v>13.164917979002881</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I28" s="1"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B29" s="1">
         <v>10</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D29" s="3">
-        <v>619.42431799999997</v>
+        <v>623.43698500000005</v>
       </c>
       <c r="E29" s="3">
-        <v>623.43698500000005</v>
+        <v>627.44965100000002</v>
       </c>
       <c r="F29" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126670000000786</v>
+        <v>4.0126659999999674</v>
       </c>
       <c r="G29" s="2">
         <f t="shared" si="3"/>
-        <v>13.164917979002881</v>
+        <v>13.164914698162622</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I29" s="1"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B30" s="1">
         <v>10</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D30" s="3">
-        <v>623.43698500000005</v>
+        <v>627.44965100000002</v>
       </c>
       <c r="E30" s="3">
-        <v>627.44965100000002</v>
+        <v>631.46231799999998</v>
       </c>
       <c r="F30" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126659999999674</v>
+        <v>4.0126669999999649</v>
       </c>
       <c r="G30" s="2">
         <f t="shared" si="3"/>
-        <v>13.164914698162622</v>
+        <v>13.164917979002508</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I30" s="1"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B31" s="1">
         <v>10</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D31" s="3">
-        <v>627.44965100000002</v>
+        <v>631.46231799999998</v>
       </c>
       <c r="E31" s="3">
-        <v>631.46231799999998</v>
+        <v>635.47498499999995</v>
       </c>
       <c r="F31" s="3">
         <f t="shared" si="2"/>
@@ -8090,81 +8023,78 @@
       <c r="H31" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I31" s="1"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B32" s="1">
         <v>10</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D32" s="3">
-        <v>631.46231799999998</v>
+        <v>635.47498499999995</v>
       </c>
       <c r="E32" s="3">
-        <v>635.47498499999995</v>
+        <v>639.48765100000003</v>
       </c>
       <c r="F32" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126669999999649</v>
+        <v>4.0126660000000811</v>
       </c>
       <c r="G32" s="2">
         <f t="shared" si="3"/>
-        <v>13.164917979002508</v>
+        <v>13.164914698162995</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I32" s="1"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B33" s="1">
         <v>10</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D33" s="3">
-        <v>635.47498499999995</v>
+        <v>639.48765100000003</v>
       </c>
       <c r="E33" s="3">
-        <v>639.48765100000003</v>
+        <v>643.50031799999999</v>
       </c>
       <c r="F33" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126660000000811</v>
+        <v>4.0126669999999649</v>
       </c>
       <c r="G33" s="2">
         <f t="shared" si="3"/>
-        <v>13.164914698162995</v>
+        <v>13.164917979002508</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I33" s="1"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B34" s="1">
         <v>10</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D34" s="3">
-        <v>639.48765100000003</v>
+        <v>643.50031799999999</v>
       </c>
       <c r="E34" s="3">
-        <v>643.50031799999999</v>
+        <v>647.51298499999996</v>
       </c>
       <c r="F34" s="3">
         <f t="shared" si="2"/>
@@ -8177,81 +8107,78 @@
       <c r="H34" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I34" s="1"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B35" s="1">
         <v>10</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D35" s="3">
-        <v>643.50031799999999</v>
+        <v>647.51298499999996</v>
       </c>
       <c r="E35" s="3">
-        <v>647.51298499999996</v>
+        <v>651.52565100000004</v>
       </c>
       <c r="F35" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126669999999649</v>
+        <v>4.0126660000000811</v>
       </c>
       <c r="G35" s="2">
         <f t="shared" si="3"/>
-        <v>13.164917979002508</v>
+        <v>13.164914698162995</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I35" s="1"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B36" s="1">
         <v>10</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D36" s="3">
-        <v>647.51298499999996</v>
+        <v>651.52565100000004</v>
       </c>
       <c r="E36" s="3">
-        <v>651.52565100000004</v>
+        <v>655.538318</v>
       </c>
       <c r="F36" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126660000000811</v>
+        <v>4.0126669999999649</v>
       </c>
       <c r="G36" s="2">
         <f t="shared" si="3"/>
-        <v>13.164914698162995</v>
+        <v>13.164917979002508</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I36" s="1"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B37" s="1">
         <v>10</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D37" s="3">
-        <v>651.52565100000004</v>
+        <v>655.538318</v>
       </c>
       <c r="E37" s="3">
-        <v>655.538318</v>
+        <v>659.55098499999997</v>
       </c>
       <c r="F37" s="3">
         <f t="shared" si="2"/>
@@ -8262,96 +8189,64 @@
         <v>13.164917979002508</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="I37" s="1"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B38" s="1">
         <v>10</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D38" s="3">
-        <v>655.538318</v>
+        <v>659.55098499999997</v>
       </c>
       <c r="E38" s="3">
-        <v>659.55098499999997</v>
+        <v>663.56365100000005</v>
       </c>
       <c r="F38" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126669999999649</v>
+        <v>4.0126660000000811</v>
       </c>
       <c r="G38" s="2">
         <f t="shared" si="3"/>
-        <v>13.164917979002508</v>
+        <v>13.164914698162995</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="I38" s="1"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B39" s="1">
         <v>10</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D39" s="3">
-        <v>659.55098499999997</v>
+        <v>663.56365100000005</v>
       </c>
       <c r="E39" s="3">
-        <v>663.56365100000005</v>
+        <v>667.57631800000001</v>
       </c>
       <c r="F39" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126660000000811</v>
+        <v>4.0126669999999649</v>
       </c>
       <c r="G39" s="2">
         <f t="shared" si="3"/>
-        <v>13.164914698162995</v>
+        <v>13.164917979002508</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="I39" s="1"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="B40" s="1">
-        <v>10</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="D40" s="3">
-        <v>663.56365100000005</v>
-      </c>
-      <c r="E40" s="3">
-        <v>667.57631800000001</v>
-      </c>
-      <c r="F40" s="3">
-        <f t="shared" si="2"/>
-        <v>4.0126669999999649</v>
-      </c>
-      <c r="G40" s="2">
-        <f t="shared" si="3"/>
-        <v>13.164917979002508</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="I40" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
